--- a/Assets/Project/Csv/Item/AdditionalTable/ItemDurableTable.xlsx
+++ b/Assets/Project/Csv/Item/AdditionalTable/ItemDurableTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\Dairy Farm\Assets\Project\Csv\Item\AdditionalTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0189FA77-7155-411D-8EED-1B4E3E18AAB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E725623B-3080-4EB4-B449-05A3B79BBAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7965" yWindow="2370" windowWidth="24675" windowHeight="8385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8700" yWindow="4560" windowWidth="24675" windowHeight="8385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>1</v>
@@ -493,7 +493,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>1010</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -504,7 +504,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>1020</v>
+        <v>20</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>3</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>1030</v>
+        <v>30</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>4</v>

--- a/Assets/Project/Csv/Item/AdditionalTable/ItemDurableTable.xlsx
+++ b/Assets/Project/Csv/Item/AdditionalTable/ItemDurableTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\Dairy Farm\Assets\Project\Csv\Item\AdditionalTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E725623B-3080-4EB4-B449-05A3B79BBAEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB06FB97-9C6D-42E5-9A12-D92A8B5FBE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8700" yWindow="4560" windowWidth="24675" windowHeight="8385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,21 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>{maxDurability/int/CHECK(VALUE &gt;= 1)}</t>
-  </si>
-  <si>
-    <t>괭이</t>
-  </si>
-  <si>
-    <t>물뿌리게</t>
-  </si>
-  <si>
-    <t>낫</t>
-  </si>
-  <si>
-    <t>낚시대</t>
   </si>
   <si>
     <t>{itemName/string/UNIQUE/NOT NULL}</t>
@@ -44,12 +32,24 @@
     <t>{itemId/int/UNIQUE/NOT NULL}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>대용량 물뿌리개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>별도 내구도를 가진 경우만 이곳에 작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 아이템의 내구도 기본값 = 100 (마지막 수정일 26.10.18)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,8 +65,24 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -82,6 +98,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -115,7 +137,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -127,6 +149,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -461,67 +487,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
+      <c r="E1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>10</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>20</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>30</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
